--- a/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/소모품수주_양식.xlsx
+++ b/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/소모품수주_양식.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,48 +29,40 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
+      <color rgb="00B01010"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="10"/>
+      <color rgb="003D3328"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="003D3328"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
+      <color rgb="006B6258"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="00B01010"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <sz val="11"/>
+      <color rgb="003D3328"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -79,12 +71,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="00F4F1E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,43 +85,49 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,97 +491,312 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>YYYY.MM  DETAIL LIST MATERIALS ORDER IN KOREA   (소모품 발주 리스트 — 드림텍 양식)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>㈜케이엔케이 (HAIST)   소모품 발주 요청서</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>고객사</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>작성일</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>담당자·연락처</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>※ 아래 표에 한 줄에 한 항목씩 적어 주세요.  ‘품목명’과 ‘개수’는 꼭 채워 주시고, 적용 모델·규격·단위·요청일은 있으면 적어 주세요.  사진은 ‘사진’ 칸에 붙여넣어도 됩니다.  (가격·납기는 ㈜케이엔케이에서 정리합니다.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>MODEL USE</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>BOM &amp;PICTURE LOCATION</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>PICTURE</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>SUPPLIER NAME (품명)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>ORDER DATE
-요청일</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Q'TY
-요청 수량</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>업체명</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>↓ 4행부터 입력하세요. 고객사(드림텍) 파일 내용을 그대로 붙여넣어도 됩니다. (품명·수량 필수)</t>
-        </is>
-      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>MODEL USE (적용 모델)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>품명 (SUPPLIER NAME)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>규격 (SPEC)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>수량 (Q'TY)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>단위 (UNIT)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>요청일 (ORDER DATE)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>사진 (PICTURE)</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
+  <mergeCells count="6">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -598,240 +806,162 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>소모품 수주 양식 — 작성안내</t>
-        </is>
-      </c>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>소모품 발주 요청서 — 작성 안내  (㈜케이엔케이 / HAIST)</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr"/>
+      <c r="B2" s="9" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>고객사(드림텍 등)가 보내온 소모품 요청 리스트를 그대로 올리는 양식입니다. 매출영업센터 → 소모품 수주 → C 소모품 등록 에서 업로드하세요.</t>
-        </is>
-      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>㈜케이엔케이가 고객사에 드리는 소모품 발주 요청 '표준 양식'입니다. 이 양식에 맞춰 작성해 회신해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr"/>
+      <c r="B4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>■ 작성 순서</t>
         </is>
       </c>
+      <c r="B5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>[소모품] 시트 4행부터 한 줄에 품목 1건씩 입력 (또는 고객사 파일 내용을 붙여넣기).</t>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>[소모품] 시트 5행부터 한 줄에 한 품목씩 입력하세요.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>품명·수량은 반드시 입력. 나머지는 있는 만큼.</t>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>품명·수량은 반드시 입력. 적용 모델·규격·단위·요청일은 있으면 입력.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>사진이 있으면 PICTURE 열(E)의 해당 줄 셀에 이미지를 붙여넣으면 자동으로 그 품목에 연결됩니다.</t>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>사진이 있으면 '사진(PICTURE)' 칸(H열)에 이미지를 붙여넣어도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>단가는 양식에 넣지 않습니다 — 업로드 후 미리보기 화면에서 입력합니다.</t>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>단가·금액·납기는 ㈜케이엔케이에서 정리하므로 비워 두셔도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>작성을 마치면 파일을 그대로 저장해 회신해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>■ 컬럼 설명</t>
-        </is>
-      </c>
+      <c r="A11" s="10" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>순번 (비워도 됨)</t>
-        </is>
-      </c>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>■ 주의</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>MODEL USE</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>적용 모델 (예: SM-A576B CTC (AUTO))</t>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>헤더 행([소모품] 시트 4행)은 바꾸지 마세요. 자동으로 인식됩니다 (NO / MODEL USE / 품명 / 규격 / 수량 / 단위 / 요청일).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>BOM &amp;PICTURE LOCATION</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>BOM/사진 위치 (선택)</t>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>품목이 많으면 행을 아래로 계속 추가하셔도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>PICTURE</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>사진 — 셀에 이미지 붙여넣기</t>
-        </is>
-      </c>
+      <c r="A15" s="10" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLIER NAME (품명)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>품명 — 필수 (각 줄의 기준)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>ORDER DATE / 요청일</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>요청일 (예: 05.06.2026 또는 2026-06-05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Q'TY / 요청 수량</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>수량 — 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>단위 (EA 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>업체명</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>요청 업체 (예: KNK)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>■ 작성 예시</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>NO=1  MODEL USE=SM-A576B CTC (AUTO)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>품명=CABLE 10 PIN-AWM 20624 80C 60V VW-1  ·  요청일=05.06.2026  ·  수량=30  ·  단위=EA  ·  업체명=KNK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>NO=2  MODEL USE=SM-A576B CTC (AUTO)</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>품명=CABLE 50 PIN 80C VW-1  ·  요청일=05.06.2026  ·  수량=30  ·  단위=EA  ·  업체명=KNK</t>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>㈜케이엔케이 (HAIST) 자재·구매 담당</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A5:B5"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/소모품수주_양식.xlsx
+++ b/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/소모품수주_양식.xlsx
@@ -2,25 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14055" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소모품" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="14">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -28,41 +27,103 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00B01010"/>
+      <color rgb="FFB01010"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="003D3328"/>
+      <color rgb="FF3D3328"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="003D3328"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF3D3328"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <i val="1"/>
-      <color rgb="006B6258"/>
+      <color rgb="FF6B6258"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00B01010"/>
+      <color rgb="FFB01010"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="003D3328"/>
+      <color rgb="FF3D3328"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF3D3328"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF3D3328"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +132,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F1E8"/>
+        <fgColor rgb="FFF4F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -85,52 +152,166 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="3">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal 78" xfId="2"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -493,310 +674,445 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" style="30" min="1" max="1"/>
+    <col width="23.375" customWidth="1" style="30" min="2" max="2"/>
+    <col width="28.75" customWidth="1" style="30" min="3" max="3"/>
+    <col width="36.125" customWidth="1" style="30" min="4" max="4"/>
+    <col width="37.25" customWidth="1" style="30" min="5" max="5"/>
+    <col width="9" customWidth="1" style="6" min="6" max="6"/>
+    <col width="12.75" customWidth="1" style="30" min="7" max="7"/>
+    <col width="18.125" customWidth="1" style="30" min="8" max="8"/>
+    <col width="26.375" customWidth="1" style="30" min="9" max="9"/>
+    <col width="22.125" customWidth="1" style="30" min="10" max="10"/>
+    <col width="25.75" customWidth="1" style="30" min="11" max="11"/>
+    <col width="5.875" customWidth="1" style="30" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>㈜케이엔케이 (HAIST)   소모품 발주 요청서</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>고객사</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>작성일</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>담당자·연락처</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="1" ht="40.5" customHeight="1" s="30">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>㈜케이엔케이 소모품 발주 요청서</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22.05" customHeight="1" s="30">
+      <c r="A2" s="17" t="n"/>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>1차 고객사</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="28" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="27" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+      <c r="J2" s="18" t="inlineStr">
+        <is>
+          <t>관리번호</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="inlineStr">
+        <is>
+          <t>(시스템 자동 등록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22.05" customHeight="1" s="30">
+      <c r="A3" s="17" t="n"/>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>2차 고객사</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="28" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="23" t="n"/>
+      <c r="G3" s="28" t="n"/>
+      <c r="H3" s="20" t="n"/>
+      <c r="I3" s="20" t="n"/>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>수주번호</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>(시스템 자동 등록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22.05" customHeight="1" s="30">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>납품위치</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="23" t="n"/>
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>프로젝트명</t>
+        </is>
+      </c>
+      <c r="K4" s="22" t="inlineStr">
+        <is>
+          <t>소모품</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>프로젝트명에는 "소모품" 으로 작성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22.05" customHeight="1" s="30">
+      <c r="A5" s="17" t="n"/>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>발주일</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>모델명</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>모델명은 "해당월 또는 주차"를 작성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22.05" customHeight="1" s="30">
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>납품일</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>장비명</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="n"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>장비명은 "소모품 XX종"을 작성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22.05" customHeight="1" s="30">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>고객사 담당자</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>KNK 담당자</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="n"/>
+    </row>
+    <row r="8" ht="22.05" customHeight="1" s="30">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>고객사 담당자 연락처</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="26" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="30">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>※ 아래 표에 한 줄에 한 항목씩 적어 주세요.  ‘품목명’과 ‘개수’는 꼭 채워 주시고, 적용 모델·규격·단위·요청일은 있으면 적어 주세요.  사진은 ‘사진’ 칸에 붙여넣어도 됩니다.  (가격·납기는 ㈜케이엔케이에서 정리합니다.)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="30">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>연결 관리번호</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>MODEL USE (적용 모델)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>품명 (SUPPLIER NAME)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>규격 (SPEC)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>수량 (Q'TY)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>단위 (UNIT)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>요청일 (ORDER DATE)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>사진(PICTURE LOCATION)</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>사진 (PICTURE)</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
+    <row r="11" ht="80" customHeight="1" s="30">
+      <c r="A11" s="31" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="80" customHeight="1" s="30">
+      <c r="A12" s="31" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="14" t="n"/>
+    </row>
+    <row r="13" ht="80" customHeight="1" s="30">
+      <c r="A13" s="31" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="80" customHeight="1" s="30">
+      <c r="A14" s="31" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="14" t="n"/>
+    </row>
+    <row r="15" ht="80" customHeight="1" s="30">
+      <c r="A15" s="31" t="n"/>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="J15" s="14" t="n"/>
+      <c r="K15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="80" customHeight="1" s="30">
+      <c r="A16" s="31" t="n"/>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="31" t="n"/>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="80" customHeight="1" s="30">
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="80" customHeight="1" s="30">
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="80" customHeight="1" s="30">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="31" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="80" customHeight="1" s="30">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="80" customHeight="1" s="30">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="31" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="16" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="80" customHeight="1" s="30">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="31" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="80" customHeight="1" s="30">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="16" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="80" customHeight="1" s="30">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="31" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A3:I3"/>
+  <mergeCells count="3">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -806,156 +1122,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="82" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" style="30" min="1" max="1"/>
+    <col width="82" customWidth="1" style="30" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>소모품 발주 요청서 — 작성 안내  (㈜케이엔케이 / HAIST)</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr"/>
+    <row r="1" ht="19.5" customHeight="1" s="30">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>소모품 발주 요청서 — 작성 안내</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr"/>
-      <c r="B2" s="9" t="inlineStr"/>
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>㈜케이엔케이가 고객사에 드리는 소모품 발주 요청 '표준 양식'입니다. 이 양식에 맞춰 작성해 회신해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr"/>
-      <c r="B4" s="9" t="inlineStr"/>
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>■ 작성 순서</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>[소모품] 시트 5행부터 한 줄에 한 품목씩 입력하세요.</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>[소모품] 시트 11행부터 한 줄에 한 품목씩 입력하세요.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>품명·수량은 반드시 입력. 적용 모델·규격·단위·요청일은 있으면 입력.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>사진이 있으면 '사진(PICTURE)' 칸(H열)에 이미지를 붙여넣어도 됩니다.</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>사진이 있으면 '사진(PICTURE)' 칸(J열)에 이미지를 붙여넣어도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>단가·금액·납기는 ㈜케이엔케이에서 정리하므로 비워 두셔도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>작성을 마치면 파일을 그대로 저장해 회신해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr"/>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>프로젝트명에는 "소모품" 으로 작성한다.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>모델명은 "해당월 또는 주차"를 작성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>장비명은 "소모품 XX종"을 작성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>■ 주의</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="B15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="26.25" customHeight="1" s="30">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>헤더 행([소모품] 시트 4행)은 바꾸지 마세요. 자동으로 인식됩니다 (NO / MODEL USE / 품명 / 규격 / 수량 / 단위 / 요청일).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>헤더 행([소모품] 시트 10행)은 바꾸지 마세요. 자동으로 인식됩니다 (NO / MODEL USE / 품명 / 규격 / 수량 / 단위 / 요청일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>품목이 많으면 행을 아래로 계속 추가하셔도 됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr"/>
-      <c r="B15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>문의</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>㈜케이엔케이 (HAIST) 자재·구매 담당</t>
         </is>

--- a/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/소모품수주_양식.xlsx
+++ b/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/소모품수주_양식.xlsx
@@ -3,20 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14055" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="43080" yWindow="-9030" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소모품" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+  </numFmts>
   <fonts count="14">
     <font>
       <name val="맑은 고딕"/>
@@ -24,14 +26,6 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FFB01010"/>
-      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -122,6 +116,14 @@
       <color rgb="FF3D3328"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFB01010"/>
+      <sz val="26"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -142,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -163,19 +165,6 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -213,99 +202,100 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -674,443 +664,489 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="5" customWidth="1" style="30" min="1" max="1"/>
     <col width="23.375" customWidth="1" style="30" min="2" max="2"/>
-    <col width="28.75" customWidth="1" style="30" min="3" max="3"/>
-    <col width="36.125" customWidth="1" style="30" min="4" max="4"/>
-    <col width="37.25" customWidth="1" style="30" min="5" max="5"/>
-    <col width="9" customWidth="1" style="6" min="6" max="6"/>
-    <col width="12.75" customWidth="1" style="30" min="7" max="7"/>
-    <col width="18.125" customWidth="1" style="30" min="8" max="8"/>
-    <col width="26.375" customWidth="1" style="30" min="9" max="9"/>
-    <col width="22.125" customWidth="1" style="30" min="10" max="10"/>
-    <col width="25.75" customWidth="1" style="30" min="11" max="11"/>
-    <col width="5.875" customWidth="1" style="30" min="12" max="12"/>
+    <col width="28.75" customWidth="1" style="30" min="3" max="4"/>
+    <col width="36.125" customWidth="1" style="30" min="5" max="5"/>
+    <col width="44.375" customWidth="1" style="30" min="6" max="6"/>
+    <col width="30.5" customWidth="1" style="30" min="7" max="7"/>
+    <col width="22.125" customWidth="1" style="30" min="8" max="8"/>
+    <col width="9" customWidth="1" style="5" min="9" max="9"/>
+    <col width="12.75" customWidth="1" style="30" min="10" max="10"/>
+    <col width="17.375" customWidth="1" style="30" min="11" max="11"/>
+    <col width="21.375" customWidth="1" style="30" min="12" max="12"/>
+    <col width="22.625" customWidth="1" style="30" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" customHeight="1" s="30">
-      <c r="A1" s="29" t="inlineStr">
+    <row r="1" ht="63.75" customHeight="1" s="30">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>㈜케이엔케이 소모품 발주 요청서</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22.05" customHeight="1" s="30">
-      <c r="A2" s="17" t="n"/>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="A2" s="15" t="n"/>
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>1차 고객사</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="28" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="27" t="n"/>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="18" t="inlineStr">
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="23" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>관리번호</t>
         </is>
       </c>
-      <c r="K2" s="21" t="inlineStr">
+      <c r="M2" s="19" t="inlineStr">
         <is>
           <t>(시스템 자동 등록)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22.05" customHeight="1" s="30">
-      <c r="A3" s="17" t="n"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>2차 고객사</t>
         </is>
       </c>
-      <c r="C3" s="22" t="n"/>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="23" t="n"/>
-      <c r="G3" s="28" t="n"/>
-      <c r="H3" s="20" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>수주번호</t>
         </is>
       </c>
-      <c r="K3" s="21" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>(시스템 자동 등록)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22.05" customHeight="1" s="30">
-      <c r="A4" s="17" t="n"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>납품위치</t>
         </is>
       </c>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="28" t="n"/>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="23" t="n"/>
-      <c r="G4" s="28" t="n"/>
-      <c r="H4" s="20" t="n"/>
-      <c r="I4" s="20" t="n"/>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>프로젝트명</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr">
+      <c r="M4" s="20" t="inlineStr">
         <is>
           <t>소모품</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>프로젝트명에는 "소모품" 으로 작성한다.</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="22.05" customHeight="1" s="30">
-      <c r="A5" s="17" t="n"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>발주일</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>모델명</t>
         </is>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>모델명은 "해당월 또는 주차"를 작성한다.</t>
-        </is>
-      </c>
+      <c r="M5" s="20" t="n"/>
     </row>
     <row r="6" ht="22.05" customHeight="1" s="30">
-      <c r="A6" s="17" t="n"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>납품일</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="28" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="28" t="n"/>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>장비명</t>
         </is>
       </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>장비명은 "소모품 XX종"을 작성한다.</t>
-        </is>
-      </c>
+      <c r="M6" s="20" t="n"/>
     </row>
     <row r="7" ht="22.05" customHeight="1" s="30">
-      <c r="A7" s="17" t="n"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>고객사 담당자</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="28" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>KNK 담당자</t>
         </is>
       </c>
-      <c r="K7" s="22" t="n"/>
+      <c r="M7" s="20" t="n"/>
     </row>
     <row r="8" ht="22.05" customHeight="1" s="30">
-      <c r="A8" s="17" t="n"/>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>고객사 담당자 연락처</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="23" t="n"/>
-      <c r="G8" s="28" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="26" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="30">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>통화</t>
+        </is>
+      </c>
+      <c r="M8" s="28" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22.05" customHeight="1" s="30">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>거래구분</t>
+        </is>
+      </c>
+      <c r="M9" s="28" t="inlineStr">
+        <is>
+          <t>내수</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="30">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>※ 아래 표에 한 줄에 한 항목씩 적어 주세요.  ‘품목명’과 ‘개수’는 꼭 채워 주시고, 적용 모델·규격·단위·요청일은 있으면 적어 주세요.  사진은 ‘사진’ 칸에 붙여넣어도 됩니다.  (가격·납기는 ㈜케이엔케이에서 정리합니다.)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="30">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="30">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>연결 관리번호</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>MODEL USE (적용 모델)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>품명 (SUPPLIER NAME)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>규격 (SPEC)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>수량 (Q'TY)</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>단위 (UNIT)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>요청일 (ORDER DATE)</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>모델명</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>장비명</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>소모품 품명</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>소모품 규격 (SPEC)</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>사진(PICTURE LOCATION)</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>사진 (PICTURE)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="K11" s="26">
+        <f>"단가 ("&amp;$M$8&amp;")"</f>
+        <v/>
+      </c>
+      <c r="L11" s="26">
+        <f>"금액 ("&amp;$M$8&amp;")"</f>
+        <v/>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1" s="30">
-      <c r="A11" s="31" t="n"/>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="14" t="n"/>
     </row>
     <row r="12" ht="80" customHeight="1" s="30">
       <c r="A12" s="31" t="n"/>
       <c r="B12" s="31" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="14" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="33" t="n"/>
+      <c r="L12" s="33" t="n"/>
+      <c r="M12" s="25" t="n"/>
     </row>
     <row r="13" ht="80" customHeight="1" s="30">
       <c r="A13" s="31" t="n"/>
       <c r="B13" s="31" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="31" t="n"/>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="14" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="33" t="n"/>
+      <c r="L13" s="33" t="n"/>
+      <c r="M13" s="25" t="n"/>
     </row>
     <row r="14" ht="80" customHeight="1" s="30">
       <c r="A14" s="31" t="n"/>
       <c r="B14" s="31" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="14" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="33" t="n"/>
+      <c r="L14" s="33" t="n"/>
+      <c r="M14" s="25" t="n"/>
     </row>
     <row r="15" ht="80" customHeight="1" s="30">
       <c r="A15" s="31" t="n"/>
       <c r="B15" s="31" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="J15" s="14" t="n"/>
-      <c r="K15" s="14" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="33" t="n"/>
+      <c r="L15" s="33" t="n"/>
+      <c r="M15" s="25" t="n"/>
     </row>
     <row r="16" ht="80" customHeight="1" s="30">
       <c r="A16" s="31" t="n"/>
       <c r="B16" s="31" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="31" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="33" t="n"/>
+      <c r="L16" s="33" t="n"/>
+      <c r="M16" s="25" t="n"/>
     </row>
     <row r="17" ht="80" customHeight="1" s="30">
       <c r="A17" s="31" t="n"/>
       <c r="B17" s="31" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="14" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="33" t="n"/>
+      <c r="L17" s="33" t="n"/>
+      <c r="M17" s="25" t="n"/>
     </row>
     <row r="18" ht="80" customHeight="1" s="30">
       <c r="A18" s="31" t="n"/>
       <c r="B18" s="31" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="33" t="n"/>
+      <c r="L18" s="33" t="n"/>
+      <c r="M18" s="25" t="n"/>
     </row>
     <row r="19" ht="80" customHeight="1" s="30">
       <c r="A19" s="31" t="n"/>
       <c r="B19" s="31" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="31" t="n"/>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="33" t="n"/>
+      <c r="L19" s="33" t="n"/>
+      <c r="M19" s="25" t="n"/>
     </row>
     <row r="20" ht="80" customHeight="1" s="30">
       <c r="A20" s="31" t="n"/>
       <c r="B20" s="31" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="14" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="33" t="n"/>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="25" t="n"/>
     </row>
     <row r="21" ht="80" customHeight="1" s="30">
       <c r="A21" s="31" t="n"/>
       <c r="B21" s="31" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="J21" s="14" t="n"/>
-      <c r="K21" s="14" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="33" t="n"/>
+      <c r="L21" s="33" t="n"/>
+      <c r="M21" s="25" t="n"/>
     </row>
     <row r="22" ht="80" customHeight="1" s="30">
       <c r="A22" s="31" t="n"/>
       <c r="B22" s="31" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="14" t="n"/>
-      <c r="K22" s="14" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="25" t="n"/>
     </row>
     <row r="23" ht="80" customHeight="1" s="30">
       <c r="A23" s="31" t="n"/>
       <c r="B23" s="31" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="J23" s="14" t="n"/>
-      <c r="K23" s="14" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="31" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="33" t="n"/>
+      <c r="L23" s="33" t="n"/>
+      <c r="M23" s="25" t="n"/>
     </row>
     <row r="24" ht="80" customHeight="1" s="30">
       <c r="A24" s="31" t="n"/>
       <c r="B24" s="31" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="14" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="33" t="n"/>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="25" t="n"/>
+    </row>
+    <row r="25" ht="80" customHeight="1" s="30">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="33" t="n"/>
+      <c r="L25" s="33" t="n"/>
+      <c r="M25" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A10:J10"/>
   </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="M8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"KRW,USD,EUR,JPY,CNY"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"내수,수출"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"KRW,USD,VND,JPY,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"내수,수출"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -1173,7 +1209,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>[소모품] 시트 11행부터 한 줄에 한 품목씩 입력하세요.</t>
+          <t>[소모품] 시트 5행부터 한 줄에 한 품목씩 입력하세요.</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1233,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>사진이 있으면 '사진(PICTURE)' 칸(J열)에 이미지를 붙여넣어도 됩니다.</t>
+          <t>사진이 있으면 '사진(PICTURE)' 칸(H열)에 이미지를 붙여넣어도 됩니다.</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1305,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>헤더 행([소모품] 시트 10행)은 바꾸지 마세요. 자동으로 인식됩니다 (NO / MODEL USE / 품명 / 규격 / 수량 / 단위 / 요청일).</t>
+          <t>헤더 행([소모품] 시트 4행)은 바꾸지 마세요. 자동으로 인식됩니다 (NO / MODEL USE / 품명 / 규격 / 수량 / 단위 / 요청일).</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/소모품수주_양식.xlsx
+++ b/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/소모품수주_양식.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -123,6 +123,40 @@
       <b val="1"/>
       <color rgb="FFB01010"/>
       <sz val="26"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B01010"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="003D3328"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="003D3328"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="003D3328"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="003D3328"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="003D3328"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -208,7 +242,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,6 +330,28 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1130,8 +1186,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A10:J10"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A10:J10"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="M8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -1158,180 +1214,280 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="30" min="1" max="1"/>
-    <col width="82" customWidth="1" style="30" min="2" max="2"/>
+    <col width="24" customWidth="1" style="30" min="1" max="1"/>
+    <col width="92" customWidth="1" style="30" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="30">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>소모품 발주 요청서 — 작성 안내</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
+    <row r="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>소모품 발주 요청서 — 작성 안내  (㈜케이엔케이 / HAIST)</t>
+        </is>
+      </c>
+      <c r="B1" s="35" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="36" t="inlineStr"/>
+      <c r="B2" s="37" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>㈜케이엔케이가 고객사에 드리는 소모품 발주 요청 '표준 양식'입니다. 이 양식에 맞춰 작성해 회신해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="2" t="n"/>
+      <c r="A4" s="36" t="inlineStr"/>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>■ 작성 순서</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>[소모품] 시트 5행부터 한 줄에 한 품목씩 입력하세요.</t>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>[소모품] 시트 12행부터 한 줄에 한 품목씩 입력하세요. (머리글은 11행)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>품명·수량은 반드시 입력. 적용 모델·규격·단위·요청일은 있으면 입력.</t>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>품명·수량은 반드시 입력. 나머지는 아래 '항목 설명'을 참고해 가능한 만큼 입력하세요.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>사진이 있으면 '사진(PICTURE)' 칸(H열)에 이미지를 붙여넣어도 됩니다.</t>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>사진은 'PICTURE LOCATION' 칸과 'PICTURE' 칸에 각각 붙여넣으세요 (아래 설명 참고).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>단가·금액·납기는 ㈜케이엔케이에서 정리하므로 비워 두셔도 됩니다.</t>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>단가·금액·통화·납기는 ㈜케이엔케이에서 정리하므로 비워 두셔도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>작성을 마치면 파일을 그대로 저장해 회신해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>프로젝트명에는 "소모품" 으로 작성한다.</t>
+      <c r="A11" s="36" t="inlineStr"/>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>모델명은 "해당월 또는 주차"를 작성한다.</t>
-        </is>
-      </c>
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>■ 항목 설명</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>장비명은 "소모품 XX종"을 작성한다.</t>
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>연결관리번호</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>이 소모품이 들어가는 '기존 제작 검사기 또는 장비'의 관리번호입니다. 향후 추적을 위해 입력합니다(알면 기재).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n"/>
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>모델명</t>
+        </is>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>고객사 아이템(제품)의 모델명.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>장비명</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>당사(㈜케이엔케이)가 제작한 장비의 명칭.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>품명 / 규격</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>소모품의 품명 / 규격(SPEC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>사진 (PICTURE LOCATION)</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>소모품이 포함되어 있는 '블럭 또는 부품'의 사진 (소모품이 어디에 쓰이는지 보여주는 위치 사진).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>사진 (PICTURE)</t>
+        </is>
+      </c>
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>해당 '소모품 자체'의 사진.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>수량 / 단위</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>요청 수량 / 단위(EA 등).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>단가 / 금액 / 통화 / 거래구분</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>㈜케이엔케이에서 정리합니다. (금액은 단가×수량, 통화·거래구분은 상단 정보란 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="inlineStr"/>
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>■ 상단 정보란</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>고객사·납품위치·발주일·납품일·고객 담당자/연락처·통화·거래구분 등을 적습니다. 관리번호·수주번호는 시스템이 자동 부여합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="inlineStr"/>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>■ 주의</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="26.25" customHeight="1" s="30">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>헤더 행([소모품] 시트 4행)은 바꾸지 마세요. 자동으로 인식됩니다 (NO / MODEL USE / 품명 / 규격 / 수량 / 단위 / 요청일).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>품목이 많으면 행을 아래로 계속 추가하셔도 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
+        <is>
+          <t>머리글 행([소모품] 시트 11행)은 바꾸지 마세요 — 그대로 두면 자동으로 인식됩니다. 품목이 많으면 행을 아래로 계속 추가하셔도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="36" t="inlineStr"/>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>문의</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>㈜케이엔케이 (HAIST) 자재·구매 담당</t>
         </is>
